--- a/utils/monday_sprint_sprint_2025-9.xlsx
+++ b/utils/monday_sprint_sprint_2025-9.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="217">
   <si>
     <t>Ticket</t>
   </si>
@@ -373,6 +373,9 @@
   </si>
   <si>
     <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -3193,21 +3196,21 @@
         <v>119</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3219,10 +3222,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3263,10 +3266,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3295,7 +3298,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3307,10 +3310,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3351,10 +3354,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3383,7 +3386,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3395,10 +3398,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>61</v>
@@ -3427,7 +3430,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3439,10 +3442,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3471,7 +3474,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3483,10 +3486,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3515,7 +3518,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3527,10 +3530,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3559,7 +3562,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3571,10 +3574,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3603,7 +3606,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3615,10 +3618,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3659,10 +3662,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3691,7 +3694,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3703,10 +3706,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3735,7 +3738,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3747,10 +3750,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>61</v>
@@ -3768,7 +3771,7 @@
         <v>17</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>26</v>
@@ -3779,7 +3782,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3791,13 +3794,13 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>17</v>
@@ -3812,7 +3815,7 @@
         <v>17</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>33</v>
@@ -3823,7 +3826,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3856,7 +3859,7 @@
         <v>17</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>33</v>
@@ -3867,7 +3870,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3879,10 +3882,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -3900,7 +3903,7 @@
         <v>17</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>33</v>
@@ -3923,10 +3926,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -3944,7 +3947,7 @@
         <v>17</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>33</v>
@@ -3955,7 +3958,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -3967,10 +3970,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -3988,7 +3991,7 @@
         <v>17</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>33</v>
@@ -3999,7 +4002,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4011,10 +4014,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4032,7 +4035,7 @@
         <v>17</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>26</v>
@@ -4043,7 +4046,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4055,10 +4058,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4076,7 +4079,7 @@
         <v>17</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4099,39 +4102,39 @@
         <v>114</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4143,34 +4146,34 @@
         <v>114</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -4187,10 +4190,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4208,7 +4211,7 @@
         <v>17</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
@@ -4219,7 +4222,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4231,10 +4234,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4252,7 +4255,7 @@
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>26</v>
@@ -4275,10 +4278,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4296,7 +4299,7 @@
         <v>17</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
@@ -4307,7 +4310,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4319,10 +4322,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4340,7 +4343,7 @@
         <v>17</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
@@ -4363,10 +4366,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4384,7 +4387,7 @@
         <v>17</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>26</v>
@@ -4407,10 +4410,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4428,7 +4431,7 @@
         <v>17</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
@@ -4439,7 +4442,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4451,10 +4454,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>61</v>
@@ -4472,7 +4475,7 @@
         <v>17</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>26</v>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4495,10 +4498,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4516,7 +4519,7 @@
         <v>17</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>26</v>
@@ -4527,22 +4530,22 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4560,7 +4563,7 @@
         <v>17</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>26</v>
@@ -4571,22 +4574,22 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4604,7 +4607,7 @@
         <v>17</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>26</v>
@@ -4615,7 +4618,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4627,10 +4630,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4648,7 +4651,7 @@
         <v>17</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>26</v>
@@ -4670,23 +4673,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4694,16 +4697,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4722,7 +4725,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4743,7 +4746,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4774,12 +4777,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B2">
         <v>80</v>
@@ -4803,25 +4806,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4838,13 +4841,13 @@
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4876,27 +4879,27 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11">
         <v>16</v>
       </c>
       <c r="P11" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -4908,19 +4911,19 @@
         <v>72</v>
       </c>
       <c r="M12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="Q12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>97</v>
       </c>
@@ -4928,27 +4931,21 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
-      <c r="P13" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13">
-        <v>17</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4962,7 +4959,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4970,7 +4967,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4978,7 +4975,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -4997,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5005,44 +5002,44 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-9.xlsx
+++ b/utils/monday_sprint_sprint_2025-9.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="250">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30784</t>
+    <t>8864818732</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>04/04/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,16 @@
     <t>Abril</t>
   </si>
   <si>
-    <t>30922</t>
+    <t>8863993761</t>
   </si>
   <si>
     <t>LISTA MODELOS LIGAS 102XX, 103XX e 104XX</t>
   </si>
   <si>
-    <t>30963</t>
+    <t>29/04/2025</t>
+  </si>
+  <si>
+    <t>8977208377</t>
   </si>
   <si>
     <t>Listar o Motivo dos Retrabalhos</t>
@@ -117,10 +120,13 @@
     <t>22/04/2025</t>
   </si>
   <si>
+    <t>04/05/2025</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>31022</t>
+    <t>8977208486</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -129,10 +135,16 @@
     <t>QlikSense Controle de Investimentos Dashboard</t>
   </si>
   <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
+    <t>8977208644</t>
+  </si>
+  <si>
     <t>QlikSense Controle de Investimentos Extração da base</t>
   </si>
   <si>
-    <t>30301</t>
+    <t>8754473310</t>
   </si>
   <si>
     <t>NOVO FLUXO 111 - ITENS COMERCIAIS COMPRADOS PELA ALTONA ENGENHARIA</t>
@@ -141,19 +153,22 @@
     <t>21/03/2025</t>
   </si>
   <si>
+    <t>03/05/2025</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>30990</t>
+    <t>8865245554</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DOS FLUXOS 100, 101, 102, 103, 108</t>
   </si>
   <si>
-    <t>31156</t>
+    <t>8955605822</t>
   </si>
   <si>
     <t>QlikSense - filtro de unidades de negócio</t>
@@ -162,55 +177,70 @@
     <t>17/04/2025</t>
   </si>
   <si>
-    <t>31236</t>
+    <t>8976542191</t>
+  </si>
+  <si>
+    <t>02/05/2025</t>
+  </si>
+  <si>
+    <t>8977291629</t>
   </si>
   <si>
     <t>ERRO: QlikSense - Aplicações de Custeio</t>
   </si>
   <si>
-    <t>31215</t>
+    <t>21/04/2025</t>
+  </si>
+  <si>
+    <t>8955130671</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE FLUXOS - ENG DE PRODUTO E APLICAÇÃO E PDM FLUXO 104</t>
   </si>
   <si>
-    <t>31212</t>
+    <t>8955168886</t>
   </si>
   <si>
     <t>Solicitação de Ajuste no WMS – Retenção do Login</t>
   </si>
   <si>
-    <t>31211</t>
+    <t>8955218534</t>
   </si>
   <si>
     <t>Solicitação de Ajustes no WMS – Tela do Picklist</t>
   </si>
   <si>
-    <t>31209</t>
+    <t>05/05/2025</t>
+  </si>
+  <si>
+    <t>8955312442</t>
   </si>
   <si>
     <t>Solicitação de ajuste no WMS - Tela de consulta da O.M.</t>
   </si>
   <si>
-    <t>31199</t>
+    <t>24/04/2025</t>
+  </si>
+  <si>
+    <t>8955336770</t>
   </si>
   <si>
     <t>Sequencias Sem Fluxo</t>
   </si>
   <si>
-    <t>31187</t>
+    <t>8955357966</t>
   </si>
   <si>
     <t>TRAVA DE INCLUSÃO DE OTF COM ALERTA DE REVISÃO EM ABERTO</t>
   </si>
   <si>
-    <t>31186</t>
+    <t>8955373082</t>
   </si>
   <si>
     <t>REVISÃO FLUXO 106</t>
   </si>
   <si>
-    <t>31185</t>
+    <t>8955383949</t>
   </si>
   <si>
     <t>Apontamento de refugo moldagem USE</t>
@@ -219,13 +249,13 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>31183</t>
+    <t>8955407579</t>
   </si>
   <si>
     <t>CADASTRO DE FORNECEDOR - NF 36234</t>
   </si>
   <si>
-    <t>31179</t>
+    <t>8955430443</t>
   </si>
   <si>
     <t>Criação de Trava para Datas de Tratamento Térmico</t>
@@ -234,109 +264,118 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>31171</t>
+    <t>8955498179</t>
   </si>
   <si>
     <t>ATUALIZAR A INFORMAÇÃO NO APONTAMENTO ELETRONICO - MOTIVO DE PARADA 174 - REUNIÃO/DSS!!</t>
   </si>
   <si>
-    <t>31166</t>
+    <t>8955539684</t>
   </si>
   <si>
     <t>Alterar registro das transferência para Data e Hora</t>
   </si>
   <si>
-    <t>31151</t>
+    <t>23/04/2025</t>
+  </si>
+  <si>
+    <t>8956024272</t>
   </si>
   <si>
     <t>Adicionar campo no registro de moldagem da UPR</t>
   </si>
   <si>
-    <t>31144</t>
-  </si>
-  <si>
-    <t>31133</t>
+    <t>8956119251</t>
+  </si>
+  <si>
+    <t>8956333497</t>
   </si>
   <si>
     <t>Relatório de materiais</t>
   </si>
   <si>
-    <t>31132</t>
+    <t>8956429732</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO TABLET MANIPULADORES</t>
   </si>
   <si>
-    <t>31131</t>
+    <t>8956442581</t>
   </si>
   <si>
     <t>Postergação Embarque 04/04</t>
   </si>
   <si>
-    <t>31123</t>
+    <t>8956455098</t>
   </si>
   <si>
     <t>Controle de consumo Aciaria</t>
   </si>
   <si>
-    <t>31106</t>
+    <t>8956464960</t>
   </si>
   <si>
     <t>WMS - Pick list</t>
   </si>
   <si>
-    <t>31102</t>
+    <t>8956477580</t>
   </si>
   <si>
     <t>Integração arquivo de suprimento de estoque</t>
   </si>
   <si>
-    <t>31097</t>
+    <t>8956486624</t>
   </si>
   <si>
     <t>[NIMBI] Ajuste no campo de integração de PROJETO e OSI para leitura individual do item versus PROJETO versus OSI</t>
   </si>
   <si>
-    <t>31094</t>
+    <t>8956497681</t>
   </si>
   <si>
     <t>[NIMBI] Espelhar o titulo da requisição do NImbi no ERP e criar campo para informar o numero requisição do Nimbi</t>
   </si>
   <si>
-    <t>31060</t>
+    <t>8956547588</t>
   </si>
   <si>
     <t>Campo na pré-análise</t>
   </si>
   <si>
-    <t>31057</t>
+    <t>8956563315</t>
   </si>
   <si>
     <t>Aplicação irog</t>
   </si>
   <si>
-    <t>31052</t>
+    <t>8956575488</t>
   </si>
   <si>
     <t>Cadastro de T.P. na CPP</t>
   </si>
   <si>
-    <t>31051</t>
+    <t>8956590348</t>
   </si>
   <si>
     <t>Cadastro Retroativo</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8957175585</t>
   </si>
   <si>
     <t>Desenvolver um check-in e status da operação</t>
   </si>
   <si>
+    <t>30/04/2025</t>
+  </si>
+  <si>
+    <t>8957179929</t>
+  </si>
+  <si>
     <t>Criar uma visão master para visualizar os horarios agendados</t>
   </si>
   <si>
-    <t>31223</t>
+    <t>8957406154</t>
   </si>
   <si>
     <t>Correção</t>
@@ -357,37 +396,31 @@
     <t>Migrar aplicações</t>
   </si>
   <si>
-    <t>21/04/2025</t>
-  </si>
-  <si>
-    <t>30903</t>
+    <t>8976468558</t>
   </si>
   <si>
     <t>Criação de Sistema de Controle impostos e declarações</t>
   </si>
   <si>
-    <t>27379</t>
+    <t>8976475308</t>
   </si>
   <si>
     <t>Interface Planilhas Custeio Gerencial x Sistema de Custeio - Reunião</t>
   </si>
   <si>
-    <t>30964</t>
+    <t>8976491133</t>
   </si>
   <si>
     <t>Integração do TDM ao sistema Altona</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>8996262896</t>
   </si>
   <si>
     <t>Ao vincular NF na invoice (no sistema Altona), atualizar esta informação no Benner</t>
   </si>
   <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
-    <t>30839</t>
+    <t>8976568244</t>
   </si>
   <si>
     <t>Etiqueta amarela</t>
@@ -396,6 +429,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -414,73 +450,85 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>30154</t>
+    <t>8976568784</t>
   </si>
   <si>
     <t>Extração de Roteiros em massa</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8976588230</t>
   </si>
   <si>
     <t>Bloco K Reroativo 2019/01 a 2023/09</t>
   </si>
   <si>
-    <t>30979</t>
+    <t>8976753897</t>
   </si>
   <si>
     <t>VPN Telemetria (Web Service) Criar Lista QR code</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>27/04/2025</t>
+  </si>
+  <si>
+    <t>8976846115</t>
   </si>
   <si>
     <t>Integração dos dados comerciais Benner  - Homologação</t>
   </si>
   <si>
-    <t>31011</t>
+    <t>8977230823</t>
   </si>
   <si>
     <t>Gestão Diário de bordo moldagem - Fast loop Carrosel e ULE</t>
   </si>
   <si>
-    <t>31113</t>
+    <t>8977275893</t>
   </si>
   <si>
     <t>ERRO E MELHORIA: Sistema de Custeio - PPR</t>
   </si>
   <si>
-    <t>31260</t>
+    <t>8982340070</t>
   </si>
   <si>
     <t>Quantidade de moldes apontados x sistema UPR</t>
   </si>
   <si>
-    <t>31307</t>
+    <t>9055399628</t>
   </si>
   <si>
     <t>Implementar processo de reivão das cotas</t>
   </si>
   <si>
-    <t>02/05/2025</t>
-  </si>
-  <si>
     <t>Maio</t>
   </si>
   <si>
+    <t>9055402589</t>
+  </si>
+  <si>
     <t>Manter a ordem de entrada das sequência na montagem do PDI</t>
   </si>
   <si>
+    <t>9055404406</t>
+  </si>
+  <si>
     <t>Criar tela de consultas das cotas registradas e seus anexos</t>
   </si>
   <si>
+    <t>9055407262</t>
+  </si>
+  <si>
     <t>Permitir cota (mínima e máxima) sem preenchimento e informata laudo.</t>
   </si>
   <si>
+    <t>9055409398</t>
+  </si>
+  <si>
     <t>Ajustar botões "MODIFICAR", "NOVA REVISÃO" e VISUALIZAR COTAS"</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>8977208207</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber) Validação</t>
@@ -489,10 +537,7 @@
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>31167</t>
+    <t>8955511566</t>
   </si>
   <si>
     <t>Página para Conta Insertos</t>
@@ -504,28 +549,34 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>31178</t>
-  </si>
-  <si>
-    <t>31070</t>
+    <t>8955441931</t>
+  </si>
+  <si>
+    <t>8956536736</t>
   </si>
   <si>
     <t>Notas no relatório do 5S</t>
   </si>
   <si>
+    <t>8956623235</t>
+  </si>
+  <si>
     <t>Integração faturamento x Benner</t>
   </si>
   <si>
-    <t>29095</t>
+    <t>8974230739</t>
   </si>
   <si>
     <t>Diário do bordo Ajustagem</t>
   </si>
   <si>
+    <t>8976491217</t>
+  </si>
+  <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>8976491274</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
@@ -534,6 +585,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
   </si>
   <si>
@@ -555,37 +609,49 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
+    <t>8996238171</t>
+  </si>
+  <si>
     <t>Enviar PROFORMA para o Benner ao enviar NF e parcelas. Informação será usada para o controle e baixa de adiantamentos</t>
   </si>
   <si>
-    <t>30476</t>
+    <t>8976566880</t>
   </si>
   <si>
     <t>Grupo de Etapa LS Carrier</t>
   </si>
   <si>
+    <t>8996255629</t>
+  </si>
+  <si>
     <t>Enviar cotação da moeda para o Benner ao faturar e integrar a NF. A partir dessa informação a variação cambial será gerada e controlada automaticamente pelo Benner (verificar layout de integração já usado no passado)</t>
   </si>
   <si>
-    <t>30019</t>
+    <t>8976568120</t>
   </si>
   <si>
     <t>Peças em carteira - Ultimo fornecimento +4 anos</t>
   </si>
   <si>
+    <t>8996268141</t>
+  </si>
+  <si>
     <t>Ao emitir a NF de exportação, dividir as parcelas conforme cadastro da proforma (CPC355A % parcelas ) ao invés de seguir a OTF</t>
   </si>
   <si>
+    <t>8996272145</t>
+  </si>
+  <si>
     <t>Atualizar retroativamente o número da proforma no Benner para documentos integrados a partir 01/01/2025</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>8977152956</t>
   </si>
   <si>
     <t>Conversão KB18 - Importação de Objetos TRN, PRC e RPT  - Homologação</t>
   </si>
   <si>
-    <t>31225</t>
+    <t>8977951858</t>
   </si>
   <si>
     <t>Alteração no Preenchimento dos Certificados no AP119</t>
@@ -609,6 +675,9 @@
     <t>Implementar login com AD</t>
   </si>
   <si>
+    <t>8996172788</t>
+  </si>
+  <si>
     <t>Implementar regra para novas contas PPR para diretoria industrial</t>
   </si>
   <si>
@@ -618,7 +687,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-9</t>
+    <t>Mar/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -673,6 +742,9 @@
   </si>
   <si>
     <t>Abertos</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1251,7 +1323,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1268,7 +1340,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1280,10 +1352,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1295,10 +1367,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1307,7 +1379,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1315,46 +1387,46 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1362,46 +1434,46 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1409,7 +1481,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1421,10 +1493,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1436,10 +1508,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1448,15 +1520,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1468,10 +1540,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1486,7 +1558,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1503,7 +1575,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1515,34 +1587,34 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1550,7 +1622,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1562,10 +1634,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1577,10 +1649,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1589,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1597,7 +1669,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1609,10 +1681,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1624,10 +1696,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1636,7 +1708,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1644,7 +1716,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1656,10 +1728,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1671,10 +1743,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1683,7 +1755,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1691,37 +1763,37 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1730,7 +1802,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1738,7 +1810,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1750,10 +1822,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1765,10 +1837,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1777,7 +1849,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1785,7 +1857,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1797,10 +1869,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1812,10 +1884,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1824,7 +1896,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1832,7 +1904,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1844,10 +1916,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1859,10 +1931,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1871,7 +1943,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1879,7 +1951,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1891,10 +1963,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1906,10 +1978,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1918,7 +1990,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1926,7 +1998,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1938,10 +2010,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1953,10 +2025,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1965,7 +2037,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1973,46 +2045,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L19" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2020,7 +2092,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2032,10 +2104,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2047,10 +2119,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2059,7 +2131,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2067,7 +2139,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2079,13 +2151,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -2094,10 +2166,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2106,7 +2178,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2114,7 +2186,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2126,10 +2198,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2141,10 +2213,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2153,7 +2225,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2161,7 +2233,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2173,10 +2245,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2188,10 +2260,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2200,7 +2272,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2208,7 +2280,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2220,13 +2292,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -2235,10 +2307,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2247,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2255,7 +2327,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2267,10 +2339,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2282,10 +2354,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2294,7 +2366,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2302,7 +2374,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2314,10 +2386,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2329,10 +2401,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2341,7 +2413,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2349,7 +2421,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2361,10 +2433,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2376,10 +2448,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2388,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2396,7 +2468,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2408,10 +2480,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2423,10 +2495,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2435,7 +2507,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2443,7 +2515,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2455,10 +2527,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2470,10 +2542,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2482,7 +2554,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2490,7 +2562,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2502,10 +2574,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2517,10 +2589,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2529,7 +2601,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2537,7 +2609,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2549,10 +2621,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2564,10 +2636,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2576,7 +2648,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2584,7 +2656,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2596,10 +2668,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2611,10 +2683,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2623,7 +2695,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2631,7 +2703,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2643,10 +2715,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2658,10 +2730,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2670,7 +2742,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2678,7 +2750,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2690,10 +2762,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2705,10 +2777,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2717,7 +2789,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2725,7 +2797,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2737,10 +2809,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2752,10 +2824,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2764,7 +2836,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2772,7 +2844,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2784,10 +2856,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2799,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>24</v>
@@ -2811,7 +2883,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2819,7 +2891,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2831,10 +2903,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2846,7 +2918,7 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
@@ -2858,7 +2930,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2866,7 +2938,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2878,10 +2950,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2893,10 +2965,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2905,7 +2977,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2913,7 +2985,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2925,10 +2997,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2940,10 +3012,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2952,7 +3024,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -2960,22 +3032,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2987,10 +3059,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2999,7 +3071,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3007,22 +3079,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3034,10 +3106,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -3046,7 +3118,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -3054,22 +3126,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3081,10 +3153,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3093,7 +3165,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -3101,7 +3173,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3113,10 +3185,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3128,10 +3200,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3140,7 +3212,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -3148,7 +3220,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3160,10 +3232,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3175,10 +3247,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3187,7 +3259,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3195,46 +3267,46 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3242,7 +3314,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3254,10 +3326,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3269,10 +3341,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3281,7 +3353,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3289,7 +3361,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3301,10 +3373,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3316,10 +3388,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3328,7 +3400,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3336,46 +3408,46 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3383,7 +3455,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3395,10 +3467,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3410,10 +3482,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3422,7 +3494,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3430,7 +3502,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3442,10 +3514,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3457,10 +3529,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3469,7 +3541,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3477,7 +3549,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3489,10 +3561,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3504,10 +3576,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3516,7 +3588,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3524,7 +3596,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3536,10 +3608,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3551,10 +3623,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3563,7 +3635,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -3571,46 +3643,46 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -3618,7 +3690,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3630,10 +3702,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3645,10 +3717,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3657,7 +3729,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -3665,7 +3737,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3677,10 +3749,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3692,19 +3764,19 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -3712,7 +3784,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3724,10 +3796,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3739,10 +3811,10 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3754,12 +3826,12 @@
         <v>27</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3771,10 +3843,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3786,10 +3858,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3801,12 +3873,12 @@
         <v>27</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3818,10 +3890,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3833,10 +3905,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3848,12 +3920,12 @@
         <v>27</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3865,10 +3937,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3880,10 +3952,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -3895,12 +3967,12 @@
         <v>27</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3912,10 +3984,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3927,10 +3999,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -3942,12 +4014,12 @@
         <v>27</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3959,13 +4031,13 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>21</v>
@@ -3974,19 +4046,19 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -3994,7 +4066,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4006,13 +4078,13 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>21</v>
@@ -4021,19 +4093,19 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -4041,7 +4113,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4053,10 +4125,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4068,19 +4140,19 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -4088,7 +4160,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4100,10 +4172,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4115,19 +4187,19 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>28</v>
@@ -4135,7 +4207,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4147,10 +4219,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4162,19 +4234,19 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>28</v>
@@ -4182,22 +4254,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4209,19 +4281,19 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>
@@ -4229,46 +4301,46 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -4276,7 +4348,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4288,10 +4360,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4303,19 +4375,19 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
@@ -4323,46 +4395,46 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>28</v>
@@ -4370,46 +4442,46 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="M70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>28</v>
@@ -4417,7 +4489,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4429,10 +4501,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4444,19 +4516,19 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>28</v>
@@ -4464,7 +4536,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4476,10 +4548,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4491,19 +4563,19 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>28</v>
@@ -4511,7 +4583,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>121</v>
+        <v>202</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4523,10 +4595,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4538,19 +4610,19 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
@@ -4558,7 +4630,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4570,10 +4642,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4585,19 +4657,19 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>28</v>
@@ -4605,7 +4677,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4617,10 +4689,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4632,19 +4704,19 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>28</v>
@@ -4652,7 +4724,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4664,10 +4736,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4679,19 +4751,19 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
@@ -4699,46 +4771,46 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="N77" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>28</v>
@@ -4746,7 +4818,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4758,10 +4830,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4773,19 +4845,19 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>28</v>
@@ -4793,22 +4865,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4820,19 +4892,19 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>28</v>
@@ -4840,22 +4912,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4867,19 +4939,19 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>28</v>
@@ -4887,7 +4959,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -4899,10 +4971,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -4914,19 +4986,19 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>28</v>
@@ -4945,23 +5017,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4969,16 +5041,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4989,15 +5061,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>393</v>
+        <v>17.76</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5010,7 +5082,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -5018,7 +5090,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5049,12 +5121,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B2">
         <v>80</v>
@@ -5068,35 +5140,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>393</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5104,7 +5176,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5113,13 +5185,13 @@
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5134,18 +5206,24 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -5154,24 +5232,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="N11">
         <v>16</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q11">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5183,53 +5267,59 @@
         <v>72</v>
       </c>
       <c r="J12" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="K12">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
+      <c r="P13" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -5237,7 +5327,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5245,7 +5335,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5253,7 +5343,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5261,10 +5351,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5272,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5280,142 +5370,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>378</v>
+        <v>439</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>32</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
